--- a/TESTS/zlit_5_bremenske.xlsx
+++ b/TESTS/zlit_5_bremenske.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Осел собака кіт і півень — чотири тварини що вирушили до Бремена стати музикантами</t>
+          <t>Осел собака кіт і півень</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Чотирьох домашніх тварин — осла собаку кота і півня — яких господарі хотіли позбутись через старість</t>
+          <t>Чотирьох домашніх тварин</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Чотири — осел собака кіт і півень — всі старі і непотрібні господарям</t>
+          <t>Чотири</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Щоб стати вуличними музикантами — кожному з них загрожувала загибель від господарів</t>
+          <t>Щоб стати вуличними музикантами</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Стати музикантами у Бремені — жити вільно і заробляти музикою</t>
+          <t>Стати музикантами у Бремені</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Будинок розбійників — вночі з вікна лилось світло і пахло їжею</t>
+          <t>Будинок розбійників</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Стали один на одного (осел — знизу, потім собака, кіт і на самому верху півнів) і заспівали всі разом</t>
+          <t>Стали один на одного (осел</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чому осел першим вирушив у дорогу до Бремена?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Господар вигнав за неслухняність</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він постарів і не міг більше носити мішки, тож господар хотів його позбутися</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він захотів пригод</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Йому наказав пес</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що осел вирішив робити в Бремені?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Тягати вози</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Стати вуличним музикантом</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Працювати на ринку</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Відпочивати</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Кого осел зустрів першим на шляху до Бремена?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Кота</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пса, що лежав при дорозі</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Півня</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Корову</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Чому пес лежав при дорозі такий виснажений?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він заблукав</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він постарів, не міг більше полювати, і господар хотів його застрелити</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він втік без причини</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він шукав їжу</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що осел запропонував псу?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишитись на дорозі</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Піти разом до Бремена і стати музикантами</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Повернутись до господаря</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Знайти нового хазяїна</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Що, за словами осла, пес міг би робити в оркестрі?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Співати</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Голосно й ритмічно гавкати, відбиваючи такт</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Грати на скрипці</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Танцювати</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Чому кіт мав такий сумний вигляд, коли осел і пес його зустріли?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він загубив іграшку</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він постарів, перестав ловити мишей, і господиня хотіла його утопити</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його вигнали за бруд</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він захворів</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як кіт описав свій настрій тваринам?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він був веселий</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Йому було не до співу, адже йому загрожувала смерть</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був голодний</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він хотів додому</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що кіт умів робити, що стало в нагоді майбутньому оркестру?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Грати на флейті</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Гарно мяукати при місячному світлі</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Танцювати</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бити в барабан</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Чому півень кричав так голосно і сумно, коли тварини його зустріли?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він радів ранку</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Наступного дня його мали зварити на суп, тож він кричав востаннє</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він кликав господаря</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він злякався лисиці</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що осел порадив півню?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Замовкнути</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Піти з ними до Бремена, бо його голос придасться оркестру</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сховатись у курнику</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Полетіти геть</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Яким голосом, за задумом тварин, півень мав співати в оркестрі?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Тихо</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дзвінко і голосно, як він уміє кричати щоранку</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Шепотом</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Жалібно</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Як тварини зазирнули у вікно будинку розбійників?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Через двері</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Стали одне на одного — осел унизу, на ньому пес, на псі кіт, а на котику півень</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Залізли по драбині</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Через трубу</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що тварини зробили одночасно, щоб налякати розбійників?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заспівали тихо</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Закричали кожен своїм голосом і ввалились крізь вікно</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Постукали у двері</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Засвітили вогонь</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як розбійники відреагували на цей раптовий «концерт» тварин?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Запросили їх за стіл</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З переляку повтікали з будинку в ліс</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покликали поліцію</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Почали танцювати</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Чому один із розбійників повернувся вночі до будинку?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Забув гроші</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Перевірити, чи можна повернутись у дім</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Захотів їсти</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Хотів забрати тварин</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Що сталося з розбійником, коли він зайшов у темну кімнату, де сидів кіт?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кіт подряпав йому обличчя, прийнявши очі за жарини</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Кіт втік</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Кіт замуркотів</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що ще сталося з розбійником, коли він тікав через двір?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він спіткнувся об камінь</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пес вкусив його за ногу, осел хвицнув копитом, а півень закричав зі стріхи</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він впав у яму</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його облив дощ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що тварини вирішили робити після того, як прогнали розбійників?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Все ж піти до Бремена</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Залишитися жити у зручному будинку розбійників</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Повернутись до старих господарів</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Спалити будинок</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чи дісталися «бременські музиканти» врешті до самого Бремена?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Так, і стали відомими</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ні, вони так і залишились жити в будинку в лісі</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Так, але повернулись</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Невідомо</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чому розбійники більше не наважились повернутись у свій будинок?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Будинок згорів</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони боялися «страшного чудовиська», яке, на їхню думку, там оселилося</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Будинок продали</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Прийшла поліція</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яку міжнародну популярність здобула казка «Бременські музиканти»?</t>
+          <t>У багатьох містах світу є пам'ятники бременським музикантам, найвідоміший — у самому Бремені.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що у Бремені нагадує про цю казку?</t>
+          <t>У Бремені встановлено бронзову скульптуру осла, пса, кота і півня, що стоять один на одному.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку народну мудрість стверджує казка «Бременські музиканти»?</t>
+          <t>Казка стверджує, що навіть ті, кого вважають старими й непотрібними, можуть досягти успіху, якщо діють разом.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Чи добрались тварини до Бремена насправді?</t>
+          <t>Тварини так і не дійшли до Бремена, бо знайшли собі дім ще в дорозі.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея казки «Бременські музиканти»?</t>
+          <t>Головна ідея казки — сила дружби та взаємодопомоги допомагає подолати будь-які труднощі.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що символізують чотири тварини у казці?</t>
+          <t>Чотири тварини символізують лише диких звірів лісу, не пов'язаних із життям людей.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,37 +2412,42 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які труднощі долали тварини на шляху до Бремена?</t>
+          <t>Що допомогло тваринам перемогти розбійників?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Старість і непотрібність господарям</t>
+          <t>Несподіваність і спільний «концерт» одночасно</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Небезпеки дороги</t>
+          <t>Те, що, ставши один на одного, вони здавались величезними</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Відсутність їжі і притулку</t>
+          <t>Магічна сила</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Зустріч з розбійниками</t>
+          <t>Гучні крики кожного своїм голосом</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>А,Б,В</t>
+          <t>А,Б,Г</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Що це якесь страхітливе чудовисько — вони кинулись тікати і назад не повернулись</t>
+          <t>Що це якесь страхітливе чудовисько</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Злякали розбійників своїм спільним «виступом» — ті втекли і більше не поверталися</t>
+          <t>Злякали розбійників своїм спільним «виступом»</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
